--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -515,6 +515,41 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 20:01:39</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-07收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>生成3条决策：买入沪深300ETF(510300)；买入紫金矿业(601899)；买入中国平安(601318)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -550,6 +550,41 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:38:14</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-08收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：买入长江电力(600900)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -585,6 +585,41 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:46:35</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>人工主动减仓：卖出紫金矿业 18200 股 @ 33.860（部分止盈）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>已按人工指令登记决策记录与交易流水，并通过规则引擎校验</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>成交价与数量由操作人提供；行情数据来自东财/腾讯公开接口</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED——人工主动决策并已成交</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>写入决策记录（07）与交易账本（09）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -620,6 +620,41 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 18:26:49</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-09收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：买入紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -655,6 +655,41 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:51:45</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-10收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -690,6 +690,41 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 18:18:19</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-10收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -725,6 +725,41 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:35:59</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-10收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -760,6 +760,41 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:51:01</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-10收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -795,6 +795,41 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:59:44</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-10收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -830,6 +830,41 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:56:19</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-11收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -865,6 +865,41 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:16:53</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-11收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -900,6 +900,41 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:38:25</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-11收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -935,6 +935,41 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 20:44:55</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-11收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -970,6 +970,41 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 20:55:12</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-11收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1005,6 +1005,41 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 14:44:40</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-11收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1040,6 +1040,41 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 15:15:41</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-11收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
